--- a/jogos_2024-10-29.xlsx
+++ b/jogos_2024-10-29.xlsx
@@ -772,16 +772,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.75</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.36</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45594.3125</v>
@@ -901,16 +901,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.36</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45594.3125</v>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['85', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.38</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['35', '64', '82']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45594.36458333334</v>
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['35', '64', '82']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.25</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['85', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45594.36458333334</v>
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.75</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['63', '78']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45594.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -1983,59 +1983,59 @@
         <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['48', '61', '70', '74']</t>
+          <t>['8', '48', '69']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,48 +2062,48 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="R13" t="n">
         <v>1.33</v>
@@ -2112,59 +2112,59 @@
         <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['8', '48', '69']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2320,75 +2320,75 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z15" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2397,19 +2397,19 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['3', '5', '86', '90+4']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['63', '78']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.73</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="P17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="AA17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['20', '55', '62']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2707,23 +2707,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.5</v>
       </c>
-      <c r="N18" t="n">
+      <c r="T18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.73</v>
       </c>
-      <c r="O18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['33', '62', '77']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>4.33</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['20', '55', '62']</t>
+          <t>['48', '61', '70', '74']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45594.58333333334</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.3</v>
       </c>
-      <c r="M20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.73</v>
       </c>
-      <c r="P20" t="n">
+      <c r="AD20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['3', '5', '86', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['33', '62', '77']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45594.58333333334</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3123,67 +3123,67 @@
         <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="T21" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
         <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3196,7 +3196,7 @@
         <v>1.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3223,48 +3223,48 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
         <v>3.4</v>
       </c>
       <c r="N22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.75</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
@@ -3288,10 +3288,10 @@
         <v>3.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
         <v>4</v>
@@ -3300,32 +3300,32 @@
         <v>1.26</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '51']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,16 +3352,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="AD23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['71', '90']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.75</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,65 +3507,65 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z24" t="n">
         <v>1.4</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['48', '90+4']</t>
+          <t>['26', '35']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.5</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.2</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.65</v>
+        <v>4.75</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.45</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>2.95</v>
-      </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['35', '51']</t>
-        </is>
-      </c>
       <c r="AG26" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.67</v>
       </c>
-      <c r="O27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="AA27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="AD27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.28</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['16', '72']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45594.60416666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45594.60416666666</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,55 +4152,55 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="P29" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X29" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AA29" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC29" t="n">
         <v>2.1</v>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['26', '35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '72']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AI29" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45594.60416666666</v>
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.48</v>
       </c>
-      <c r="O30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45594.60416666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,19 +4384,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P31" t="n">
         <v>2.1</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.83</v>
-      </c>
       <c r="Q31" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="R31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.62</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['71', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.77</v>
+        <v>3.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45594.60416666666</v>
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="W32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="Z32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['48', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.11</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45594.60416666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
         <v>3.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X33" t="n">
         <v>2.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB33" t="n">
         <v>1.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI33" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45594.6875</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.1</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="U35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R35" t="n">
+      <c r="Z35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['30', '45+1']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['12', '64']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.44</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45594.6875</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2.25</v>
       </c>
-      <c r="M36" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['51', '57', '66']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['16', '51']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['29', '37']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45594.6875</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="X37" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI37" t="n">
         <v>2</v>
       </c>
-      <c r="Z37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45594.6875</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,19 +5287,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
         <v>2.05</v>
@@ -5325,49 +5325,49 @@
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T38" t="n">
-        <v>2.29</v>
+        <v>3.25</v>
       </c>
       <c r="U38" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="X38" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5376,20 +5376,20 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['51', '57', '66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45594.6875</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5431,63 +5431,63 @@
         <v>2</v>
       </c>
       <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="M39" t="n">
         <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z39" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.01</v>
+        <v>3.7</v>
       </c>
       <c r="AB39" t="n">
         <v>1.25</v>
@@ -5496,29 +5496,29 @@
         <v>1.83</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['30', '45+1']</t>
+          <t>['16', '51']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['12', '64']</t>
+          <t>['29', '37']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45594.6875</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,22 +5571,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="R40" t="n">
         <v>1.44</v>
@@ -5595,59 +5595,59 @@
         <v>2.6</v>
       </c>
       <c r="T40" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.35</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB40" t="n">
         <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45594.6875</v>
@@ -5674,16 +5674,16 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -5700,65 +5700,65 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M41" t="n">
         <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V41" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI41" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45594.6875</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P42" t="n">
         <v>2.05</v>
       </c>
       <c r="Q42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T42" t="n">
         <v>2.88</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X42" t="n">
         <v>3.25</v>
       </c>
-      <c r="U42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA42" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '60']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '59']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="n">
         <v>1.3</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45594.6875</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
         <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AB43" t="n">
         <v>1.25</v>
       </c>
       <c r="AC43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD43" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['69', '90+1', '90+5']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45594.6875</v>
@@ -6061,19 +6061,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI44" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['36', '60']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['32', '59']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45594.6875</v>
@@ -6190,16 +6190,16 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O45" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
         <v>1.4</v>
@@ -6240,41 +6240,41 @@
         <v>2.75</v>
       </c>
       <c r="T45" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X45" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['54', '67', '87']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6283,16 +6283,16 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45594.6875</v>
@@ -6448,16 +6448,16 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -6474,22 +6474,22 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O47" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R47" t="n">
         <v>1.4</v>
@@ -6498,41 +6498,41 @@
         <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U47" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X47" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['54', '67', '87']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45594.6875</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,109 +6577,109 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T48" t="n">
         <v>3</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O48" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.25</v>
       </c>
       <c r="U48" t="n">
         <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X48" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AB48" t="n">
         <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['69', '90+1', '90+5']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45594.6875</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="P49" t="n">
         <v>2.1</v>
@@ -6750,65 +6750,65 @@
         <v>4.33</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T49" t="n">
         <v>3</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W49" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="X49" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['18', '33', '42', '68']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AH49" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['33', '61']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['18', '90+8']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AI49" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45594.69791666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
         <v>1</v>
       </c>
-      <c r="H50" t="n">
-        <v>4</v>
-      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T50" t="n">
         <v>3.5</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V50" t="n">
         <v>1.07</v>
       </c>
       <c r="W50" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X50" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Y50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC50" t="n">
         <v>2</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AD50" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA50" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['13', '16', '61', '88']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AI50" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45594.69791666666</v>
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Legnago Salus</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="M51" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N51" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="O51" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S51" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T51" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U51" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V51" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W51" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X51" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC51" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['11', '63']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45594.69791666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,25 +7093,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M52" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O52" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="P52" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q52" t="n">
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="U52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.25</v>
       </c>
-      <c r="V52" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AC52" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['2', '48', '90+3']</t>
+          <t>['42', '44']</t>
         </is>
       </c>
       <c r="AG52" t="n">
         <v>1.22</v>
       </c>
       <c r="AH52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI52" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45594.69791666666</v>
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>1</v>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,22 +7248,22 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="M53" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="O53" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P53" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R53" t="n">
         <v>1.5</v>
@@ -7272,10 +7272,10 @@
         <v>2.5</v>
       </c>
       <c r="T53" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U53" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
         <v>1.07</v>
@@ -7287,10 +7287,10 @@
         <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA53" t="n">
         <v>4.2</v>
@@ -7306,25 +7306,25 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
+          <t>['7', '56', '71']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
       <c r="AG53" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45594.69791666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M54" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="O54" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="R54" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T54" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W54" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X54" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC54" t="n">
         <v>1.91</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['11', '63']</t>
+          <t>['18', '88']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45594.69791666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,109 +7609,109 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>3</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>3.35</v>
-      </c>
       <c r="M56" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N56" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O56" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R56" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T56" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U56" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V56" t="n">
         <v>1.07</v>
       </c>
       <c r="W56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X56" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>['13', '16', '61', '88']</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.42</v>
       </c>
-      <c r="X56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['7', '56', '71']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI56" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45594.69791666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Legnago Salus</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,22 +7893,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="M58" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="P58" t="n">
         <v>2.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R58" t="n">
         <v>1.4</v>
@@ -7917,59 +7917,59 @@
         <v>2.75</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U58" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V58" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X58" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Z58" t="n">
         <v>1.75</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['18', '33', '42', '68']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45594.69791666666</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T59" t="n">
         <v>3</v>
       </c>
-      <c r="N59" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O59" t="n">
-        <v>5</v>
-      </c>
-      <c r="P59" t="n">
+      <c r="U59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>['33', '61']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>['18', '90+8']</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH59" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q59" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T59" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X59" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AI59" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45594.69791666666</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,25 +8125,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.73</v>
+        <v>4.1</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O60" t="n">
+        <v>5</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA60" t="n">
         <v>4.6</v>
       </c>
-      <c r="O60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X60" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB60" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['18', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.17</v>
+        <v>1.95</v>
       </c>
       <c r="AH60" t="n">
-        <v>2.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="AJ60" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45594.69791666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,25 +8254,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="P61" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q61" t="n">
         <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S61" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T61" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="U61" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V61" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W61" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X61" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.65</v>
+        <v>4.65</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['42', '44']</t>
+          <t>['2', '48', '90+3']</t>
         </is>
       </c>
       <c r="AG61" t="n">
         <v>1.22</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45594.69791666666</v>
@@ -8383,109 +8383,109 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4</v>
+      </c>
+      <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P62" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R62" t="n">
         <v>1.57</v>
       </c>
       <c r="S62" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="T62" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U62" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V62" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W62" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X62" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['16', '59', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ62" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45594.79166666666</v>
@@ -8512,23 +8512,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>1</v>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="M63" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="P63" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="R63" t="n">
         <v>1.57</v>
       </c>
       <c r="S63" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X63" t="n">
         <v>2.37</v>
       </c>
-      <c r="T63" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V63" t="n">
+      <c r="Y63" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1.11</v>
       </c>
-      <c r="W63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X63" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC63" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
+          <t>['16', '59', '72']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
       <c r="AG63" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45594.79166666666</v>
